--- a/documentation/java/JavaInterviewQuestions.xlsx
+++ b/documentation/java/JavaInterviewQuestions.xlsx
@@ -5,15 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspaces/universal-dev-suite/documentation/java/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace/universal-dev-suite/documentation/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1340" yWindow="1000" windowWidth="28760" windowHeight="17300" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="3380" yWindow="9820" windowWidth="23580" windowHeight="17300" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Problems" sheetId="2" r:id="rId1"/>
-    <sheet name="Solutions" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="150000" concurrentCalc="0"/>
   <extLst>
@@ -28,12 +27,122 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Write a java method signature only which can accept both an Array and an List and return sorted values</t>
   </si>
   <si>
-    <t>&lt;T extends Comparable&lt;? super T&gt;&gt; List&lt;T&gt; sort(Collection&lt;T&gt; input);</t>
+    <t>What happen if we add null key in HashMap, LinkedHashMap and TreeMap?</t>
+  </si>
+  <si>
+    <t>How to make a class Immutability in Java?</t>
+  </si>
+  <si>
+    <t>What is volatile keyword in Java?</t>
+  </si>
+  <si>
+    <t>Changes to a variable are always visible to other threads. So other threads cannot cache its value.</t>
+  </si>
+  <si>
+    <t>public static &lt;T extends Comparable&lt;? super T&gt;&gt; List&lt;T&gt; sort(Collection&lt;T&gt; input);
+public static &lt;T extends Comparable&lt;T&gt;&gt; List&lt;T&gt; sortItems(Object input)</t>
+  </si>
+  <si>
+    <t>HashMap, LinkedHashMap will allow null key but TreeMap will not allow Null Keys</t>
+  </si>
+  <si>
+    <t>What microservices design pattern?</t>
+  </si>
+  <si>
+    <t>Constructor, Setter, Field Injection</t>
+  </si>
+  <si>
+    <t>What are types of Dependency Injection?</t>
+  </si>
+  <si>
+    <t>Fetch=FetchType.LAZY and Fetch=FetchType.EAGER in JPA</t>
+  </si>
+  <si>
+    <t>How to optimze slow Query?</t>
+  </si>
+  <si>
+    <t>Add proper indexes</t>
+  </si>
+  <si>
+    <t>What is N+1 Select problem?</t>
+  </si>
+  <si>
+    <t>How to perform Pagination and Sorting in Spring Data JPA?</t>
+  </si>
+  <si>
+    <t>Explain Thread Pool</t>
+  </si>
+  <si>
+    <t>SOLID Principles</t>
+  </si>
+  <si>
+    <t>Singleton Design Pattern</t>
+  </si>
+  <si>
+    <t>What is Master Slave Architecture?</t>
+  </si>
+  <si>
+    <t>Master: Writes and Updates Slave: Read Operation</t>
+  </si>
+  <si>
+    <t>What happen if master dies? Slave will be promoted to Master?</t>
+  </si>
+  <si>
+    <t>Hibernate load() vs get()</t>
+  </si>
+  <si>
+    <t>Class Loaders in Java?</t>
+  </si>
+  <si>
+    <t>Bootstrap, Platform, Application ClassLoader</t>
+  </si>
+  <si>
+    <t>How can we ensure thread safety in Java?</t>
+  </si>
+  <si>
+    <t>What are best practices for handling transactions in microservices?</t>
+  </si>
+  <si>
+    <t>1. Asynchronous Commuication (Kafka, RabbitMQ)</t>
+  </si>
+  <si>
+    <t>Order -&gt; Payment -&gt; Inventory</t>
+  </si>
+  <si>
+    <t>SAGA Pattern</t>
+  </si>
+  <si>
+    <t>What is Outbox Pattern?</t>
+  </si>
+  <si>
+    <t>OrderService -&gt; RestaurantService -&gt; PaymentService -&gt; DeliveryService</t>
+  </si>
+  <si>
+    <t>Primary Billing Account
+Virtual Card Number</t>
+  </si>
+  <si>
+    <t>Where actual details are replaced with a Token. Merchant will store the actual token.</t>
+  </si>
+  <si>
+    <t>Card Tokenization / Tokenization in Microservices</t>
+  </si>
+  <si>
+    <t>Optimistic and Pessimistic Mechanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimistic Locking: (Version Number + Timestamp) Open for all Transactions every time it reads and reads versionNo for each if other transaction update then update versionNumber and Timestamp
+Pessimistic Locking: Explicitly Lock DB or Table iteself only for Current Transaction and Other have to wait
+READ UNCOMMITED
+READ COMMITTED
+Repeatable Reads
+Serializable Isolation
+</t>
   </si>
 </sst>
 </file>
@@ -69,8 +178,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -348,33 +460,169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="96.1640625" customWidth="1"/>
+    <col min="2" max="2" width="93.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="64" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="128" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
